--- a/RoHS/PolyKybd-RoHS-Compliance-Matrix.xlsx
+++ b/RoHS/PolyKybd-RoHS-Compliance-Matrix.xlsx
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -111,11 +111,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,6 +184,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,14 +632,14 @@
           <t>ELECTRICAL COMPONENTS (populated BOM)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -808,7 +854,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>4.7uF 3216 25V Tantalum</t>
+          <t>4.7uF 3216 25V Tantalum (293D475X9025A2TE3)</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -816,22 +862,22 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Sunlord</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>sunlord-rohs.pdf</t>
+          <t>vishay-rohs-20250901.pdf</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer Declaration of Conformity (RoHS + halogen + REACH)</t>
+          <t>Manufacturer RoHS Compliance Statement, 1 Sep 2025, signed COO</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>RoHS 2011/65/EU as amended by (EU) 2015/863</t>
+          <t>RoHS 2002/95/EG, 2011/65/EU, 2015/863/EU (RoHS I-III)</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -839,7 +885,11 @@
           <t>Documented</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Replaced EOL Sunlord C118249 with Vishay C5380411 (v3.3). The E3 termination suffix is Vishay's lead-free code; the 293D datasheet specifies 100% matte tin terminations.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -880,7 +930,11 @@
           <t>Documented</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Blanket 'all our MLCCs' declaration (p.2). The v3.3 part CL10C6R8CB8NNNC (C318672) is not named anywhere in the document, and the superseded CL10C6R8DB8NNNC appears on p.14 which the current appendix page selection (1,2,13,19,25) does not include. Same category as Silergy: linkage via the reference table and section divider. Consider adding p.14.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -2118,7 +2172,11 @@
           <t>Documented</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Statement is company-wide across all Nexperia semiconductor products. Its exemption appendix (p.3) lists 37 packages relying on RoHS exemptions 7(a)/7(c)-I; DHVQFN-16 is NOT among them, so this part is compliant outright. Part recoded C3303719 -&gt; C730243 in v3.3 (same MPN, 74HC595BQ,115).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -2128,7 +2186,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>W25Q64JVXGIQ</t>
+          <t>W25Q64JVXGIM</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
@@ -2136,7 +2194,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>winbond</t>
+          <t>Winbond</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2151,15 +2209,19 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>RoHS 2011/65/EU as amended by (EU) 2015/863</t>
+          <t>RoHS 2002/95/EU (as cited by the evidence)</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Documented</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr"/>
+          <t>Documented - directive version outdated</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>ACTION: the evidence is p.59 of the W25Q64JV datasheet and its RoHS note cites 2002/95/EU, which is superseded by 2011/65/EU + (EU) 2015/863. Request a current declaration from Winbond. Coverage of the part itself is fine: the document is titled W25Q64JV (the family), so it covers XGIM exactly as it covered XGIQ. Part changed C2940195 -&gt; C5440778 in v3.3.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -2246,12 +2308,12 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>U12-U23,U?,U?</t>
+          <t>U12-U25</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>SN74LVC1G126DBVR</t>
+          <t>74AHC1G125GW,125</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
@@ -2259,17 +2321,17 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>sn74lvc1g126.pdf</t>
+          <t>Nexperia - Statement on RoHS 20241008.pdf</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Manufacturer datasheet (TI SN74LVC1G126, RoHS stated)</t>
+          <t>Manufacturer RoHS statement</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -2284,7 +2346,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>TI SN74LVC1G126 datasheet (RoHS stated). Each package houses two buffers, which accounts for the designator/qty count.</t>
+          <t>Retargeted from the EOL TI C151890 to Nexperia C85397 in v3.3, so the TI datasheet no longer applies and sn74lvc1g126.pdf was deleted. Covered by the company-wide Nexperia statement; SOT-353 is NOT in its lead-exemption appendix, so compliant outright. One buffer per package: qty 14 = U12-U25, and the old 'U?,U?' placeholders are resolved.</t>
         </is>
       </c>
     </row>
@@ -2376,14 +2438,14 @@
           <t>BARE PCB (substrate, incl. exposed copper of mounting holes &amp; test points)</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="5" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="11" t="n"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -2438,14 +2500,14 @@
           <t>SCOPED OUT - no separate RoHS certificate required</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="11" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -2606,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2621,6 +2683,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2674,12 +2737,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>RESOLVED - U12-U23 (SN74LVC1G126DBVR)</t>
+          <t>RESOLVED - U12-U25 (74AHC1G125GW,125)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Re-pointed to sn74lvc1g126.pdf (TI datasheet for the correct part, RoHS stated). Housekeeping remains: two unnamed designators 'U?,U?' and qty 14 vs 12 for U12-U23.</t>
+          <t>Part retargeted from the EOL TI SN74LVC1G126DBVR (C151890) to Nexperia 74AHC1G125GW,125 (C85397) in v3.3. Evidence re-pointed to the company-wide Nexperia RoHS statement, which cites 2011/65/EU + (EU) 2015/863; SOT-353 is not in its lead-exemption appendix. sn74lvc1g126.pdf deleted. The 'U?,U?' designator placeholders are resolved - the row now reads U12-U25, qty 14.</t>
         </is>
       </c>
     </row>
@@ -2755,6 +2818,36 @@
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>The /RoHS folder also contains certs not linked in the reference table (e.g. Aerosemi MT9700, Fenghua RC-02W, Prosperity MCS0530, Uniroyal 0603WAF). Confirm whether these belong to alternates/DNPs or should be linked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OPEN - U9 (W25Q64JVXGIM)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The Winbond RoHS evidence cites directive 2002/95/EU, which is superseded by 2011/65/EU as amended by (EU) 2015/863. Request a current declaration. Part coverage is not in question - the document is family-level (W25Q64JV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OPEN - C5, C11 (CL10C6R8CB8NNNC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The v3.3 Samsung part is not named in its blanket MLCC declaration, and the superseded part is on p.14 which the appendix page selection omits. Either add p.14 and accept blanket-only coverage (consistent with how Silergy/SY6280AAC is handled) or request a part-specific declaration.</t>
         </is>
       </c>
     </row>
